--- a/reports/pdf_change_20260722.xlsx
+++ b/reports/pdf_change_20260722.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,237억   ·   현금 65억(1.5%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 10종목  /  매도 12종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 10종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>418475200</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -690,8 +692,10 @@
       <c r="H6" s="15" t="n">
         <v>-26</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-419120000</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
       <c r="B7" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>1262816000</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,8 +740,10 @@
       <c r="H7" s="15" t="n">
         <v>-23</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-825939200</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -757,8 +765,10 @@
       <c r="B8" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>2142720000</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -778,8 +788,10 @@
       <c r="H8" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-426560000</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -795,23 +807,25 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>404140800</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -822,8 +836,10 @@
       <c r="H9" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-667814400</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -839,23 +855,25 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>1201113600</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>3.97%→4.24%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -866,8 +884,10 @@
       <c r="H10" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-830304000</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -883,44 +903,48 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>423782400</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>3.97%→4.24%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-418723200</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.90%</t>
+          <t>0.39%→0.25%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -933,8 +957,10 @@
       <c r="B12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>425568000</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -948,23 +974,25 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-359004800</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.25%</t>
+          <t>0.58%→0.46%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -977,8 +1005,10 @@
       <c r="B13" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>437273600</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -992,23 +1022,25 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-393030400</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.46%</t>
+          <t>1.03%→0.90%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1021,8 +1053,10 @@
       <c r="B14" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>843200000</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1042,8 +1076,10 @@
       <c r="H14" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-399280000</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1065,8 +1101,10 @@
       <c r="B15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>746976000</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1086,8 +1124,10 @@
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-412473600</v>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1114,8 +1154,10 @@
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-363072000</v>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1142,8 +1184,10 @@
       <c r="H17" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>-324979200</v>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1159,7 +1203,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,823억   ·   현금 14억(0.4%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1254,8 +1298,10 @@
       <c r="B22" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>1855299600</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1275,8 +1321,10 @@
       <c r="H22" s="15" t="n">
         <v>-138</v>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>-7517577600</v>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1298,8 +1346,10 @@
       <c r="B23" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>1120932000</v>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1326,8 +1376,10 @@
       <c r="B24" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>1080424800</v>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1354,8 +1406,10 @@
       <c r="B25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>1906632000</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1382,8 +1436,10 @@
       <c r="B26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>1083975000</v>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1404,7 +1460,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,434억   ·   현금 47억(1.9%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1499,8 +1555,10 @@
       <c r="B31" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>4573320000</v>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1520,8 +1578,10 @@
       <c r="H31" s="15" t="n">
         <v>-200</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>-4933500000</v>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1537,7 +1597,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,246억   ·   현금 28억(1.2%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1561,7 +1621,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 -0억      당일 2026-07-22  vs  전영업일 2026-07-21      매수 6종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 6종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1656,12 +1716,14 @@
       <c r="B39" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>58851520</v>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>6.84%→6.98%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1677,12 +1739,14 @@
       <c r="H39" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I39" s="15" t="n">
-        <v>-76884000</v>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.02%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1700,12 +1764,14 @@
       <c r="B40" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>25155000</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.35%→0.43%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1721,12 +1787,14 @@
       <c r="H40" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-49260800</v>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>1.19%→1.03%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1744,12 +1812,14 @@
       <c r="B41" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>93791600</v>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>6.03%→6.29%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1772,12 +1842,14 @@
       <c r="B42" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>62350000</v>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.86%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1800,12 +1872,14 @@
       <c r="B43" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>56656800</v>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>7.27%→7.40%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1828,12 +1902,14 @@
       <c r="B44" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>39594400</v>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.77%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1850,7 +1926,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 0억(0.1%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>

--- a/reports/pdf_change_20260722.xlsx
+++ b/reports/pdf_change_20260722.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 10종목  /  매도 12종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,306억   ·   현금 64억(1.5%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 10종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,10 +669,8 @@
       <c r="B6" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="11" t="n">
+        <v>416365950</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -692,10 +690,8 @@
       <c r="H6" s="15" t="n">
         <v>-26</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="15" t="n">
+        <v>-417007500</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -717,10 +713,8 @@
       <c r="B7" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="11" t="n">
+        <v>1256451000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -740,10 +734,8 @@
       <c r="H7" s="15" t="n">
         <v>-23</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="15" t="n">
+        <v>-821776200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -765,10 +757,8 @@
       <c r="B8" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="11" t="n">
+        <v>2131920000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -788,10 +778,8 @@
       <c r="H8" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="15" t="n">
+        <v>-424410000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -807,25 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="11" t="n">
+        <v>402103800</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -836,10 +822,8 @@
       <c r="H9" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="15" t="n">
+        <v>-664448400</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -855,25 +839,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>1195059600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>3.97%→4.24%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -884,10 +866,8 @@
       <c r="H10" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="15" t="n">
+        <v>-826119000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -903,25 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="11" t="n">
+        <v>421646400</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>3.97%→4.24%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -932,10 +910,8 @@
       <c r="H11" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="15" t="n">
+        <v>-357195300</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -957,10 +933,8 @@
       <c r="B12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="11" t="n">
+        <v>423423000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -974,25 +948,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="15" t="n">
+        <v>-416612700</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.46%</t>
+          <t>1.03%→0.90%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1005,10 +977,8 @@
       <c r="B13" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="11" t="n">
+        <v>435069600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1022,25 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="15" t="n">
+        <v>-391049400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.90%</t>
+          <t>0.58%→0.46%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1053,10 +1021,8 @@
       <c r="B14" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="11" t="n">
+        <v>838950000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1076,10 +1042,8 @@
       <c r="H14" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="15" t="n">
+        <v>-397267500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1101,10 +1065,8 @@
       <c r="B15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="11" t="n">
+        <v>743211000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1118,25 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>-361242000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.14%</t>
+          <t>1.22%→1.05%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1148,25 +1108,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="15" t="n">
+        <v>-410394600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.22%→1.05%</t>
+          <t>2.30%→2.14%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1142,8 @@
       <c r="H17" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="15" t="n">
+        <v>-323341200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1203,7 +1159,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,742억   ·   현금 14억(0.4%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1298,10 +1254,8 @@
       <c r="B22" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="11" t="n">
+        <v>1848924000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1321,10 +1275,8 @@
       <c r="H22" s="15" t="n">
         <v>-138</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="15" t="n">
+        <v>-7491744000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1346,10 +1298,8 @@
       <c r="B23" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="11" t="n">
+        <v>1117080000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1376,10 +1326,8 @@
       <c r="B24" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="11" t="n">
+        <v>1076712000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1406,10 +1354,8 @@
       <c r="B25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="11" t="n">
+        <v>1900080000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1436,10 +1382,8 @@
       <c r="B26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="11" t="n">
+        <v>1080250000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1460,7 +1404,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,467억   ·   현금 47억(1.9%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1555,10 +1499,8 @@
       <c r="B31" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="11" t="n">
+        <v>4553436000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1578,10 +1520,8 @@
       <c r="H31" s="15" t="n">
         <v>-200</v>
       </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="15" t="n">
+        <v>-4912050000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1597,7 +1537,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,226억   ·   현금 27억(1.2%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1621,7 +1561,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 6종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 -0억(-0.1%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 6종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1716,14 +1656,12 @@
       <c r="B39" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="11" t="n">
+        <v>52008320</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.84%→6.98%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1739,14 +1677,12 @@
       <c r="H39" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="15" t="n">
+        <v>-67944000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.27%→1.02%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1764,14 +1700,12 @@
       <c r="B40" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="11" t="n">
+        <v>22230000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.35%→0.43%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1787,14 +1721,12 @@
       <c r="H40" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="15" t="n">
+        <v>-43532800</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.19%→1.03%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1812,14 +1744,12 @@
       <c r="B41" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="11" t="n">
+        <v>82885600</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.03%→6.29%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1842,14 +1772,12 @@
       <c r="B42" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="11" t="n">
+        <v>55100000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.68%→2.86%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1872,14 +1800,12 @@
       <c r="B43" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="11" t="n">
+        <v>50068800</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.27%→7.40%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1902,14 +1828,12 @@
       <c r="B44" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="11" t="n">
+        <v>34990400</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.66%→2.77%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1926,7 +1850,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 469억   ·   현금 0억(0.1%)      당일 2026-07-22  vs  전영업일 2026-07-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>

--- a/reports/pdf_change_20260722.xlsx
+++ b/reports/pdf_change_20260722.xlsx
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-391049400</v>
+        <v>-397267500</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.46%</t>
+          <t>0.97%→0.85%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>141→127</t>
         </is>
       </c>
     </row>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-397267500</v>
+        <v>-391049400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.97%→0.85%</t>
+          <t>0.58%→0.46%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>141→127</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1657,11 +1657,11 @@
         <v>91</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>52008320</v>
+        <v>51385880</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>6.84%→6.98%</t>
+          <t>6.76%→6.90%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1678,11 +1678,11 @@
         <v>-10</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-67944000</v>
+        <v>-67488000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.02%</t>
+          <t>1.26%→1.01%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1701,11 +1701,11 @@
         <v>90</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>22230000</v>
+        <v>23461200</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.35%→0.43%</t>
+          <t>0.37%→0.45%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1722,11 +1722,11 @@
         <v>-8</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-43532800</v>
+        <v>-47180800</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>1.19%→1.03%</t>
+          <t>1.29%→1.11%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1745,11 +1745,11 @@
         <v>38</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>82885600</v>
+        <v>80719600</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>6.03%→6.29%</t>
+          <t>5.88%→6.13%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1773,11 +1773,11 @@
         <v>25</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>55100000</v>
+        <v>54625000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.86%</t>
+          <t>2.66%→2.84%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1801,11 +1801,11 @@
         <v>18</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>50068800</v>
+        <v>49521600</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>7.27%→7.40%</t>
+          <t>7.20%→7.33%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1829,11 +1829,11 @@
         <v>4</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>34990400</v>
+        <v>35294400</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>2.66%→2.77%</t>
+          <t>2.69%→2.80%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
